--- a/src/Examples/示例工资表数据.xlsx
+++ b/src/Examples/示例工资表数据.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Develop\Personal\SendMultipleEmails\Src\Examples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Develop\Personal\uzon-mail\src\Examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{170EF454-D217-4725-8982-DDDE9FEC6369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34429BF-04B6-4806-AF2A-62D047153B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E6AEB633-E97D-45B2-8DAE-805D7115E41F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="49">
   <si>
     <t>人员编号</t>
   </si>
@@ -188,14 +188,6 @@
   </si>
   <si>
     <t>260827400@qq.com</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>收件人1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>收件人2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -213,7 +205,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>收件箱(必填)</t>
+    <t>inbox</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -742,7 +735,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
@@ -847,16 +840,14 @@
         <v>31</v>
       </c>
       <c r="AK1" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>100</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>47</v>
-      </c>
+      <c r="B2" s="6"/>
       <c r="C2" s="5">
         <v>3450</v>
       </c>
@@ -971,9 +962,7 @@
       <c r="A3" s="4">
         <v>100</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>48</v>
-      </c>
+      <c r="B3" s="6"/>
       <c r="C3" s="5">
         <v>3000</v>
       </c>
